--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4446" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -512,10 +512,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-valid-system-local-prescriptionID:jp-core-0002:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {exists(system.substring(0,31) = 'urn:oid:1.2.392.100495.20.3.11.').not() or exists(system.substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$')).not()}</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -529,24 +525,6 @@
   </si>
   <si>
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -568,9 +546,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
@@ -587,9 +562,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.use</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.use</t>
   </si>
   <si>
@@ -618,9 +590,6 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -657,16 +626,13 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.system</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -675,31 +641,29 @@
     <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
-  </si>
-  <si>
     <t>Identifier.system</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$')}</t>
+  </si>
+  <si>
     <t>II.root or Role.id.root</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.value</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -709,9 +673,6 @@
   </si>
   <si>
     <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -736,9 +697,6 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.assigner</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
@@ -764,6 +722,63 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.system</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.value</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.assigner</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier:orderInRp</t>
   </si>
   <si>
@@ -848,25 +863,10 @@
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>identifier値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
     <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.period</t>
@@ -2417,7 +2417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO111"/>
+  <dimension ref="A1:AO119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3735,40 +3735,38 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>91</v>
@@ -3783,17 +3781,15 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3842,34 +3838,34 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -3877,18 +3873,18 @@
         <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3900,15 +3896,17 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3945,31 +3943,31 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
@@ -3978,7 +3976,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3989,44 +3987,46 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -4050,43 +4050,43 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4095,21 +4095,21 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4126,25 +4126,25 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4169,13 +4169,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4193,7 +4193,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4214,21 +4214,21 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4251,7 +4251,7 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>194</v>
@@ -4288,66 +4288,66 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AK16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4370,26 +4370,24 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4431,7 +4429,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4452,21 +4450,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4474,7 +4472,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
@@ -4489,17 +4487,15 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4548,7 +4544,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4569,21 +4565,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4606,15 +4602,17 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4663,7 +4661,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4684,29 +4682,31 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
@@ -4718,19 +4718,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4780,13 +4780,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4795,37 +4795,35 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>237</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4840,17 +4838,15 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>240</v>
+        <v>163</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4899,53 +4895,53 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4957,15 +4953,17 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5002,31 +5000,31 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -5035,7 +5033,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -5046,44 +5044,46 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5107,43 +5107,43 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5152,21 +5152,21 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5183,25 +5183,25 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5226,13 +5226,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5250,7 +5250,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5271,21 +5271,21 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>91</v>
@@ -5308,13 +5308,13 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>196</v>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>82</v>
@@ -5345,31 +5345,31 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5390,21 +5390,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5427,26 +5427,24 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5488,7 +5486,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5509,21 +5507,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5531,7 +5529,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5546,17 +5544,15 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5605,7 +5601,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5626,21 +5622,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5663,15 +5659,17 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5720,7 +5718,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5741,29 +5739,31 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5775,19 +5775,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5837,13 +5837,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5852,31 +5852,29 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>237</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5885,7 +5883,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5897,17 +5895,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>258</v>
+        <v>163</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5956,53 +5952,53 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -6014,15 +6010,17 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6059,31 +6057,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6092,7 +6090,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6103,44 +6101,46 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6164,43 +6164,43 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6209,21 +6209,21 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6240,25 +6240,25 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6283,13 +6283,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6307,7 +6307,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6328,21 +6328,21 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -6365,13 +6365,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>196</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6402,31 +6402,31 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6447,21 +6447,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6484,26 +6484,24 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6545,7 +6543,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6566,21 +6564,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6588,7 +6586,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6603,17 +6601,15 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6662,7 +6658,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6683,21 +6679,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6720,15 +6716,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6777,7 +6775,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6798,23 +6796,25 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6832,19 +6832,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6894,13 +6894,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6909,31 +6909,29 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>237</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6954,17 +6952,15 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7013,53 +7009,53 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7071,15 +7067,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7116,31 +7114,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7149,7 +7147,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7160,44 +7158,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7221,43 +7221,43 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7266,21 +7266,21 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7297,25 +7297,25 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7340,13 +7340,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7364,7 +7364,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7385,21 +7385,21 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7422,7 +7422,7 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>194</v>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7459,31 +7459,31 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7504,21 +7504,21 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7541,26 +7541,24 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7602,7 +7600,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7623,21 +7621,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7645,7 +7643,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
@@ -7660,17 +7658,15 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7719,7 +7715,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7740,21 +7736,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7777,15 +7773,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7834,7 +7832,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7855,23 +7853,25 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7889,19 +7889,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7951,13 +7951,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7966,27 +7966,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>237</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>288</v>
+        <v>161</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -8003,23 +8003,21 @@
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>289</v>
+        <v>163</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8044,13 +8042,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8068,10 +8066,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>288</v>
+        <v>165</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>91</v>
@@ -8080,19 +8078,19 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>296</v>
+        <v>166</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8100,21 +8098,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>298</v>
+        <v>167</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8126,16 +8124,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>299</v>
+        <v>168</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8161,52 +8159,52 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>298</v>
+        <v>171</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>305</v>
+        <v>166</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8217,10 +8215,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>306</v>
+        <v>172</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8228,7 +8226,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>91</v>
@@ -8246,15 +8244,17 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>307</v>
+        <v>173</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>308</v>
+        <v>174</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8278,13 +8278,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>310</v>
+        <v>178</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8302,10 +8302,10 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>306</v>
+        <v>180</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>91</v>
@@ -8317,27 +8317,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>313</v>
+        <v>181</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8348,7 +8348,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8357,21 +8357,23 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>316</v>
+        <v>184</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>317</v>
+        <v>185</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8395,11 +8397,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>319</v>
+        <v>190</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8417,13 +8421,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>315</v>
+        <v>191</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8435,24 +8439,24 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>321</v>
+        <v>181</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8460,7 +8464,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
@@ -8475,24 +8479,26 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>324</v>
+        <v>195</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8510,13 +8516,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8534,7 +8540,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>322</v>
+        <v>198</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8549,27 +8555,27 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>329</v>
+        <v>200</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>285</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8577,7 +8583,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
@@ -8586,22 +8592,22 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>332</v>
+        <v>162</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>333</v>
+        <v>203</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>334</v>
+        <v>204</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>335</v>
+        <v>205</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8651,7 +8657,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>331</v>
+        <v>206</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8672,21 +8678,21 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>337</v>
+        <v>209</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8709,13 +8715,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>338</v>
+        <v>210</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>339</v>
+        <v>211</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>340</v>
+        <v>212</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8766,7 +8772,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>337</v>
+        <v>213</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8787,21 +8793,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>341</v>
+        <v>214</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>287</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>342</v>
+        <v>216</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8809,7 +8815,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
@@ -8824,16 +8830,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>343</v>
+        <v>218</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>344</v>
+        <v>219</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>345</v>
+        <v>220</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8859,13 +8865,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8883,10 +8889,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>342</v>
+        <v>221</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8898,27 +8904,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>350</v>
+        <v>222</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>352</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8935,22 +8941,22 @@
         <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>354</v>
+        <v>111</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>357</v>
+        <v>291</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8976,13 +8982,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9000,7 +9006,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9015,27 +9021,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>358</v>
+        <v>294</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>359</v>
+        <v>295</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>360</v>
+        <v>296</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>298</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>298</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9058,16 +9064,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>364</v>
+        <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>365</v>
+        <v>299</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>367</v>
+        <v>300</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9093,13 +9099,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9117,7 +9123,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>298</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9132,27 +9138,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>369</v>
+        <v>305</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9160,31 +9166,31 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>373</v>
+        <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>374</v>
+        <v>307</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9210,13 +9216,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9234,13 +9240,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9249,16 +9255,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>377</v>
+        <v>312</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>378</v>
+        <v>313</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9266,10 +9272,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>315</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>315</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9277,10 +9283,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9289,18 +9295,20 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>380</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>381</v>
+        <v>316</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9325,13 +9333,11 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9349,13 +9355,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>315</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9364,27 +9370,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>385</v>
+        <v>321</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>386</v>
+        <v>314</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>322</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>322</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9407,16 +9413,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>389</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>390</v>
+        <v>323</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>391</v>
+        <v>324</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9442,13 +9448,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9466,7 +9472,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>322</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9481,16 +9487,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>392</v>
+        <v>328</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>393</v>
+        <v>330</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9498,10 +9504,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9518,22 +9524,22 @@
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>395</v>
+        <v>332</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>396</v>
+        <v>333</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>376</v>
+        <v>335</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9583,7 +9589,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9598,16 +9604,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>399</v>
+        <v>336</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9615,10 +9621,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9641,17 +9647,15 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>339</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9676,11 +9680,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9698,7 +9704,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9713,13 +9719,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>407</v>
+        <v>341</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9730,10 +9736,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9741,7 +9747,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>91</v>
@@ -9753,19 +9759,19 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>409</v>
+        <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>411</v>
+        <v>344</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9791,13 +9797,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9815,10 +9821,10 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>91</v>
@@ -9830,27 +9836,27 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>412</v>
+        <v>350</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>413</v>
+        <v>351</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>414</v>
+        <v>353</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>353</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9858,10 +9864,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9870,19 +9876,19 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>193</v>
+        <v>354</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9908,13 +9914,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9932,13 +9938,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>414</v>
+        <v>353</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9947,27 +9953,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>420</v>
+        <v>358</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>422</v>
+        <v>360</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>423</v>
+        <v>361</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>424</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>425</v>
+        <v>363</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,7 +9984,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9990,16 +9996,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>426</v>
+        <v>364</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>428</v>
+        <v>366</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10049,13 +10055,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>425</v>
+        <v>363</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10064,27 +10070,27 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>430</v>
+        <v>368</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>295</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>431</v>
+        <v>369</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10104,19 +10110,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>436</v>
+        <v>376</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10166,7 +10172,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10181,16 +10187,16 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10198,10 +10204,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10209,10 +10215,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10224,17 +10230,15 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>105</v>
+        <v>380</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>440</v>
+        <v>381</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10283,13 +10287,13 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
@@ -10298,27 +10302,27 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>438</v>
+        <v>385</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>388</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10329,7 +10333,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10341,13 +10345,13 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>443</v>
+        <v>389</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>444</v>
+        <v>390</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>391</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>376</v>
@@ -10400,13 +10404,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>442</v>
+        <v>388</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10415,16 +10419,16 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>446</v>
+        <v>392</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10432,10 +10436,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10455,21 +10459,21 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>395</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>449</v>
+        <v>396</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10517,7 +10521,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10532,16 +10536,16 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>452</v>
+        <v>398</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>453</v>
+        <v>399</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10549,10 +10553,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>454</v>
+        <v>401</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>454</v>
+        <v>401</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10572,19 +10576,19 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>455</v>
+        <v>402</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>457</v>
+        <v>404</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10612,11 +10616,9 @@
       <c r="X70" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Y70" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10634,7 +10636,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>454</v>
+        <v>401</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10649,13 +10651,13 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>460</v>
+        <v>407</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10666,10 +10668,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10680,7 +10682,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10692,13 +10694,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>463</v>
+        <v>410</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>464</v>
+        <v>411</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>376</v>
@@ -10751,13 +10753,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>408</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10766,16 +10768,16 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>466</v>
+        <v>412</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10783,10 +10785,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>414</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10809,16 +10811,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>468</v>
+        <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>469</v>
+        <v>415</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>470</v>
+        <v>416</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10844,13 +10846,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10868,7 +10870,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>414</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10883,27 +10885,27 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>474</v>
+        <v>422</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10926,16 +10928,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>476</v>
+        <v>426</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>477</v>
+        <v>427</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>477</v>
+        <v>428</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>478</v>
+        <v>429</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10985,7 +10987,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11000,16 +11002,16 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>479</v>
+        <v>431</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11017,10 +11019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11031,7 +11033,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11040,18 +11042,20 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>481</v>
+        <v>433</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>482</v>
+        <v>434</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11100,13 +11104,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11115,13 +11119,13 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11132,10 +11136,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>439</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11146,7 +11150,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11155,18 +11159,20 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11215,19 +11221,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>172</v>
+        <v>439</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11236,7 +11242,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>173</v>
+        <v>438</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11247,10 +11253,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11270,18 +11276,20 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>443</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>490</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11318,17 +11326,19 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>179</v>
+        <v>442</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11340,16 +11350,16 @@
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11360,14 +11370,12 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11376,7 +11384,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11385,19 +11393,21 @@
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>494</v>
+        <v>150</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>495</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>496</v>
+        <v>450</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11445,28 +11455,28 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>179</v>
+        <v>448</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11477,14 +11487,12 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11505,15 +11513,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>500</v>
+        <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>501</v>
+        <v>455</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11538,13 +11548,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11562,19 +11572,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>179</v>
+        <v>454</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11583,7 +11593,7 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11594,14 +11604,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11614,26 +11624,24 @@
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>137</v>
+        <v>462</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>505</v>
+        <v>463</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11681,7 +11689,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>507</v>
+        <v>461</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11693,16 +11701,16 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>134</v>
+        <v>466</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11713,10 +11721,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>508</v>
+        <v>467</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>508</v>
+        <v>467</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11727,7 +11735,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11739,16 +11747,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>509</v>
+        <v>469</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>511</v>
+        <v>471</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11798,13 +11806,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>508</v>
+        <v>467</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -11813,13 +11821,13 @@
         <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11830,10 +11838,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11844,7 +11852,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11856,15 +11864,17 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>169</v>
+        <v>476</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>170</v>
+        <v>477</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11913,19 +11923,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>172</v>
+        <v>475</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11934,7 +11944,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>173</v>
+        <v>479</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11945,21 +11955,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -11971,17 +11981,15 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>481</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>138</v>
+        <v>482</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12030,28 +12038,28 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>179</v>
+        <v>480</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>173</v>
+        <v>485</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12062,46 +12070,42 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12149,19 +12153,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>507</v>
+        <v>165</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12170,7 +12174,7 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12181,10 +12185,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12195,7 +12199,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12207,17 +12211,15 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>517</v>
+        <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>518</v>
+        <v>490</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12254,31 +12256,29 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>516</v>
+        <v>171</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>521</v>
+        <v>142</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12287,23 +12287,25 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>524</v>
+        <v>492</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12312,7 +12314,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12324,17 +12326,15 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>525</v>
+        <v>494</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>526</v>
+        <v>495</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12383,19 +12383,19 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>524</v>
+        <v>171</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12404,7 +12404,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12415,12 +12415,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12441,17 +12443,15 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12500,19 +12500,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>529</v>
+        <v>171</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12521,7 +12521,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12532,45 +12532,45 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>535</v>
+        <v>140</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>536</v>
+        <v>146</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12619,28 +12619,28 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>532</v>
+        <v>507</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>538</v>
+        <v>134</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12651,10 +12651,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>508</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>539</v>
+        <v>508</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12677,15 +12677,17 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>169</v>
+        <v>481</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>170</v>
+        <v>509</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12734,7 +12736,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>172</v>
+        <v>508</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12746,7 +12748,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12755,7 +12757,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>173</v>
+        <v>512</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12766,21 +12768,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>513</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>513</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12792,17 +12794,15 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12839,31 +12839,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12872,7 +12872,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12883,21 +12883,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -12906,19 +12906,19 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>380</v>
+        <v>137</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>542</v>
+        <v>138</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>543</v>
+        <v>168</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>544</v>
+        <v>140</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12968,19 +12968,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>545</v>
+        <v>171</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -12989,61 +12989,61 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>547</v>
+        <v>166</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>549</v>
+        <v>515</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>549</v>
+        <v>515</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>380</v>
+        <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>550</v>
+        <v>505</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>551</v>
+        <v>506</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" t="s" s="2">
-        <v>553</v>
-      </c>
+      <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13087,19 +13087,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>554</v>
+        <v>507</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13108,21 +13108,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>555</v>
+        <v>134</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13145,16 +13145,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>558</v>
+        <v>517</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>559</v>
+        <v>518</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>560</v>
+        <v>519</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>561</v>
+        <v>520</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13204,7 +13204,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13213,33 +13213,33 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>103</v>
+        <v>521</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>563</v>
+        <v>522</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>564</v>
+        <v>523</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>565</v>
+        <v>524</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>565</v>
+        <v>524</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13262,13 +13262,13 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>566</v>
+        <v>526</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>520</v>
@@ -13321,7 +13321,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>565</v>
+        <v>524</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13330,10 +13330,10 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>521</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13342,21 +13342,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13382,13 +13382,13 @@
         <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>570</v>
+        <v>531</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>571</v>
+        <v>520</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13438,7 +13438,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13456,10 +13456,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>573</v>
+        <v>528</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13470,10 +13470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>574</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>574</v>
+        <v>532</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13496,16 +13496,20 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>170</v>
+        <v>533</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13553,7 +13557,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>172</v>
+        <v>532</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13565,16 +13569,16 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>173</v>
+        <v>538</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13585,21 +13589,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>575</v>
+        <v>539</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>575</v>
+        <v>539</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13611,17 +13615,15 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13658,31 +13660,31 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13691,7 +13693,7 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13702,21 +13704,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>576</v>
+        <v>540</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>576</v>
+        <v>540</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13725,23 +13727,21 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>577</v>
+        <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>578</v>
+        <v>138</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>579</v>
+        <v>168</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13777,31 +13777,31 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>582</v>
+        <v>171</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13810,21 +13810,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>583</v>
+        <v>166</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>584</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>585</v>
+        <v>541</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>585</v>
+        <v>541</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13841,30 +13841,28 @@
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>111</v>
+        <v>380</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>586</v>
+        <v>542</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q98" t="s" s="2">
-        <v>589</v>
-      </c>
+      <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13884,13 +13882,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13908,7 +13906,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>592</v>
+        <v>545</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13917,7 +13915,7 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>103</v>
@@ -13929,21 +13927,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>593</v>
+        <v>547</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>594</v>
+        <v>548</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>595</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>595</v>
+        <v>549</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13966,24 +13964,26 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>169</v>
+        <v>380</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>596</v>
+        <v>550</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q99" s="2"/>
+      <c r="Q99" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="R99" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14025,7 +14025,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>600</v>
+        <v>554</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14034,7 +14034,7 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -14046,21 +14046,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>601</v>
+        <v>555</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>602</v>
+        <v>556</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>603</v>
+        <v>557</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>603</v>
+        <v>557</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14080,27 +14080,27 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>558</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>604</v>
+        <v>559</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14142,7 +14142,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>608</v>
+        <v>557</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14151,7 +14151,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14160,24 +14160,24 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>610</v>
+        <v>563</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>602</v>
+        <v>564</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14197,29 +14197,27 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>111</v>
+        <v>517</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>612</v>
+        <v>566</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>613</v>
+        <v>567</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>615</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14261,7 +14259,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>617</v>
+        <v>565</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14270,10 +14268,10 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>103</v>
+        <v>521</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14282,21 +14280,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>618</v>
+        <v>522</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>602</v>
+        <v>523</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14319,16 +14317,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>620</v>
+        <v>525</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>621</v>
+        <v>569</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>622</v>
+        <v>570</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>376</v>
+        <v>571</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14378,7 +14376,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14396,13 +14394,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>623</v>
+        <v>573</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14410,10 +14408,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>624</v>
+        <v>574</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>624</v>
+        <v>574</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14436,13 +14434,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>481</v>
+        <v>162</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>625</v>
+        <v>163</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>626</v>
+        <v>164</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14493,7 +14491,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>624</v>
+        <v>165</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14505,16 +14503,16 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>628</v>
+        <v>166</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14525,21 +14523,21 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>629</v>
+        <v>575</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>629</v>
+        <v>575</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14551,15 +14549,17 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14596,31 +14596,31 @@
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -14629,7 +14629,7 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -14640,21 +14640,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>630</v>
+        <v>576</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>630</v>
+        <v>576</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -14663,21 +14663,23 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>137</v>
+        <v>577</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>138</v>
+        <v>578</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>176</v>
+        <v>579</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14725,19 +14727,19 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>179</v>
+        <v>582</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
@@ -14746,32 +14748,32 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>173</v>
+        <v>583</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -14783,24 +14785,24 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>505</v>
+        <v>586</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>146</v>
+        <v>588</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q106" s="2"/>
+      <c r="Q106" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="R106" t="s" s="2">
         <v>82</v>
       </c>
@@ -14820,13 +14822,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -14844,19 +14846,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>507</v>
+        <v>592</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -14865,21 +14867,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>134</v>
+        <v>593</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>632</v>
+        <v>595</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>632</v>
+        <v>595</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14887,7 +14889,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>91</v>
@@ -14899,27 +14901,27 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>625</v>
+        <v>596</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>82</v>
@@ -14937,11 +14939,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14959,10 +14963,10 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>632</v>
+        <v>600</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>91</v>
@@ -14977,24 +14981,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>636</v>
+        <v>601</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>637</v>
+        <v>602</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>638</v>
+        <v>603</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>638</v>
+        <v>603</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15014,27 +15018,27 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>639</v>
+        <v>604</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>82</v>
@@ -15052,13 +15056,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>642</v>
+        <v>82</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>643</v>
+        <v>82</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15076,7 +15080,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>638</v>
+        <v>608</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15085,7 +15089,7 @@
         <v>91</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>103</v>
@@ -15094,24 +15098,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>645</v>
+        <v>610</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>646</v>
+        <v>602</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>647</v>
+        <v>611</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>647</v>
+        <v>611</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15131,27 +15135,29 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>648</v>
+        <v>111</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>649</v>
+        <v>612</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>650</v>
+        <v>613</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>82</v>
@@ -15193,7 +15199,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>647</v>
+        <v>617</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15208,38 +15214,38 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>651</v>
+        <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>652</v>
+        <v>618</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>653</v>
+        <v>619</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>653</v>
+        <v>619</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15251,16 +15257,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>655</v>
+        <v>620</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>656</v>
+        <v>621</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>657</v>
+        <v>622</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>658</v>
+        <v>376</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15310,13 +15316,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>653</v>
+        <v>619</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15331,10 +15337,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>659</v>
+        <v>623</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15342,10 +15348,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>660</v>
+        <v>624</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>660</v>
+        <v>624</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15356,7 +15362,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15368,17 +15374,15 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>661</v>
+        <v>481</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>662</v>
+        <v>625</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>664</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15427,13 +15431,13 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>660</v>
+        <v>624</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
@@ -15442,18 +15446,952 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y115" s="2"/>
+      <c r="Z115" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK119" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="AN111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO111" t="s" s="2">
+      <c r="AN119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO119" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4446" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -512,6 +512,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -525,6 +529,24 @@
   </si>
   <si>
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -546,6 +568,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.extension</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
@@ -562,6 +587,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.use</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.use</t>
   </si>
   <si>
@@ -590,6 +618,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -626,13 +657,16 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.system</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>identifier値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -641,29 +675,31 @@
     <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
+  </si>
+  <si>
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$')}</t>
-  </si>
-  <si>
     <t>II.root or Role.id.root</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.value</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -673,6 +709,9 @@
   </si>
   <si>
     <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -697,6 +736,9 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:rpNumber.assigner</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
@@ -722,63 +764,6 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.system</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.value</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.assigner</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier:orderInRp</t>
   </si>
   <si>
@@ -863,10 +848,25 @@
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
   </si>
   <si>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.period</t>
@@ -2417,7 +2417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO119"/>
+  <dimension ref="A1:AO111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3735,38 +3735,40 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>91</v>
@@ -3781,15 +3783,17 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3838,34 +3842,34 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -3873,18 +3877,18 @@
         <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3896,17 +3900,15 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3943,31 +3945,31 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
@@ -3976,7 +3978,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3987,46 +3989,44 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -4050,43 +4050,43 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AC14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4095,21 +4095,21 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4126,25 +4126,25 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4169,31 +4169,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4214,21 +4214,21 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>192</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4251,7 +4251,7 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>194</v>
@@ -4288,13 +4288,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4312,7 +4312,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4324,7 +4324,7 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -4333,21 +4333,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4370,24 +4370,26 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4429,7 +4431,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4450,21 +4452,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4472,7 +4474,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
@@ -4487,15 +4489,17 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4544,7 +4548,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4565,21 +4569,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4602,17 +4606,15 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4661,7 +4663,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4682,31 +4684,29 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
@@ -4718,19 +4718,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4780,13 +4780,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4795,35 +4795,37 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>160</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4838,15 +4840,17 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>163</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4895,53 +4899,53 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4953,17 +4957,15 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5000,31 +5002,31 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -5033,7 +5035,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -5044,46 +5046,44 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5107,43 +5107,43 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="AC23" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AD23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AA23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5152,21 +5152,21 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5183,25 +5183,25 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5226,31 +5226,31 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5271,21 +5271,21 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>192</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>91</v>
@@ -5308,13 +5308,13 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>196</v>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>82</v>
@@ -5345,13 +5345,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5369,7 +5369,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5390,21 +5390,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5427,24 +5427,26 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5486,7 +5488,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5507,21 +5509,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5529,7 +5531,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5544,15 +5546,17 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5601,7 +5605,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5622,21 +5626,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5659,17 +5663,15 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5718,7 +5720,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5739,31 +5741,29 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5775,19 +5775,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5837,13 +5837,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5852,29 +5852,31 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>160</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5883,7 +5885,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5895,15 +5897,17 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>163</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5952,53 +5956,53 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -6010,17 +6014,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6057,31 +6059,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6090,7 +6092,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6101,46 +6103,44 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6164,43 +6164,43 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="AC32" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6209,21 +6209,21 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6240,25 +6240,25 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6283,31 +6283,31 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6328,21 +6328,21 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>192</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -6365,13 +6365,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>196</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6402,13 +6402,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6426,7 +6426,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6447,21 +6447,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6484,24 +6484,26 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6543,7 +6545,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6564,21 +6566,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6586,7 +6588,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6601,15 +6603,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6658,7 +6662,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6679,21 +6683,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6716,17 +6720,15 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6775,7 +6777,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6796,25 +6798,23 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6832,19 +6832,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6894,13 +6894,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6909,29 +6909,31 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>160</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6952,15 +6954,17 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>163</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7009,53 +7013,53 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7067,17 +7071,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7114,31 +7116,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7147,7 +7149,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7158,46 +7160,44 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7221,43 +7221,43 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y41" t="s" s="2">
+      <c r="AC41" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Z41" t="s" s="2">
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7266,21 +7266,21 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7297,25 +7297,25 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7340,31 +7340,31 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7385,21 +7385,21 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>192</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7422,7 +7422,7 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>194</v>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7459,13 +7459,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7483,7 +7483,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7504,21 +7504,21 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7541,24 +7541,26 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7600,7 +7602,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7621,21 +7623,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7643,7 +7645,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
@@ -7658,15 +7660,17 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7715,7 +7719,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7736,21 +7740,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7773,17 +7777,15 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7832,7 +7834,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7853,25 +7855,23 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7889,19 +7889,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7951,13 +7951,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7966,27 +7966,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>160</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>161</v>
+        <v>288</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -8003,21 +8003,23 @@
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>163</v>
+        <v>289</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8042,13 +8044,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8066,10 +8068,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>165</v>
+        <v>288</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>91</v>
@@ -8078,19 +8080,19 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>166</v>
+        <v>296</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8098,21 +8100,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>167</v>
+        <v>298</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8124,16 +8126,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>168</v>
+        <v>299</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8159,52 +8161,52 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>171</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>166</v>
+        <v>305</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8215,10 +8217,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>172</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8226,7 +8228,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>91</v>
@@ -8244,17 +8246,15 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>173</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8278,13 +8278,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>178</v>
+        <v>310</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>179</v>
+        <v>311</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8302,10 +8302,10 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>180</v>
+        <v>306</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>91</v>
@@ -8317,27 +8317,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>181</v>
+        <v>313</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>182</v>
+        <v>315</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8348,7 +8348,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8357,23 +8357,21 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>184</v>
+        <v>316</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>185</v>
+        <v>317</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8397,13 +8395,11 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>190</v>
+        <v>319</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8421,13 +8417,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>191</v>
+        <v>315</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8439,24 +8435,24 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>181</v>
+        <v>321</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8464,7 +8460,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
@@ -8479,26 +8475,24 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>195</v>
+        <v>324</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8516,13 +8510,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8540,7 +8534,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>198</v>
+        <v>322</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8555,27 +8549,27 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>200</v>
+        <v>329</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8583,7 +8577,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
@@ -8592,22 +8586,22 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>162</v>
+        <v>332</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>203</v>
+        <v>333</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>204</v>
+        <v>334</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>205</v>
+        <v>335</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8657,7 +8651,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>206</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8678,21 +8672,21 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>207</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>286</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>209</v>
+        <v>337</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8715,13 +8709,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>210</v>
+        <v>338</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>211</v>
+        <v>339</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>212</v>
+        <v>340</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8772,7 +8766,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>213</v>
+        <v>337</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8793,21 +8787,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>287</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>216</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8815,7 +8809,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
@@ -8830,16 +8824,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>218</v>
+        <v>343</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>219</v>
+        <v>344</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8865,13 +8859,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8889,10 +8883,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>221</v>
+        <v>342</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8904,27 +8898,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>222</v>
+        <v>350</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>223</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8941,22 +8935,22 @@
         <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>111</v>
+        <v>354</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>289</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>290</v>
+        <v>356</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>291</v>
+        <v>357</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8982,13 +8976,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9006,7 +9000,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9021,27 +9015,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>296</v>
+        <v>360</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>298</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>298</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9064,16 +9058,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>183</v>
+        <v>364</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>299</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>299</v>
+        <v>366</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>300</v>
+        <v>367</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9099,13 +9093,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9123,7 +9117,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>298</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9138,27 +9132,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>305</v>
+        <v>369</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9166,31 +9160,31 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>111</v>
+        <v>373</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>307</v>
+        <v>374</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>308</v>
+        <v>375</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>309</v>
+        <v>376</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9216,13 +9210,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9240,13 +9234,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9255,16 +9249,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>312</v>
+        <v>377</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>313</v>
+        <v>378</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>314</v>
+        <v>370</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9272,10 +9266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>315</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>315</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9283,10 +9277,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9295,20 +9289,18 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>183</v>
+        <v>380</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>316</v>
+        <v>381</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9333,11 +9325,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9355,13 +9349,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>315</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9370,27 +9364,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>321</v>
+        <v>385</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>314</v>
+        <v>386</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>322</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>322</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9413,16 +9407,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>111</v>
+        <v>389</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>323</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>324</v>
+        <v>391</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9448,13 +9442,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9472,7 +9466,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>322</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9487,16 +9481,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>328</v>
+        <v>392</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9504,10 +9498,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9524,22 +9518,22 @@
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>333</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9589,7 +9583,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9604,16 +9598,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9621,10 +9615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9647,15 +9641,17 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>338</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9680,13 +9676,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9704,7 +9698,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9719,13 +9713,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>341</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9736,10 +9730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>342</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>342</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9747,7 +9741,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>91</v>
@@ -9759,19 +9753,19 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>183</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>343</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>344</v>
+        <v>411</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9797,13 +9791,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9821,10 +9815,10 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>342</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>91</v>
@@ -9836,27 +9830,27 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>350</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9864,10 +9858,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9876,19 +9870,19 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>354</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9914,13 +9908,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9938,13 +9932,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9953,27 +9947,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>358</v>
+        <v>420</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>360</v>
+        <v>422</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>361</v>
+        <v>423</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>362</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9984,7 +9978,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9996,16 +9990,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>364</v>
+        <v>426</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>367</v>
+        <v>429</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10055,13 +10049,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10070,27 +10064,27 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>368</v>
+        <v>430</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>295</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>369</v>
+        <v>431</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10110,19 +10104,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10172,7 +10166,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10187,16 +10181,16 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10204,10 +10198,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10215,10 +10209,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10230,15 +10224,17 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>380</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10287,13 +10283,13 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
@@ -10302,27 +10298,27 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10333,7 +10329,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10345,13 +10341,13 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>389</v>
+        <v>443</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>390</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>391</v>
+        <v>445</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>376</v>
@@ -10404,13 +10400,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10419,16 +10415,16 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>392</v>
+        <v>446</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>360</v>
+        <v>447</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10436,10 +10432,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10459,21 +10455,21 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>395</v>
+        <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10521,7 +10517,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10536,16 +10532,16 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>398</v>
+        <v>452</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>399</v>
+        <v>453</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10553,10 +10549,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>401</v>
+        <v>454</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>401</v>
+        <v>454</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10576,19 +10572,19 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>402</v>
+        <v>455</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>403</v>
+        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10616,9 +10612,11 @@
       <c r="X70" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Y70" s="2"/>
+      <c r="Y70" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>405</v>
+        <v>459</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10636,7 +10634,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>401</v>
+        <v>454</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10651,13 +10649,13 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10668,10 +10666,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>408</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>408</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10682,7 +10680,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10694,13 +10692,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>409</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>410</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>411</v>
+        <v>464</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>376</v>
@@ -10753,13 +10751,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>408</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10768,16 +10766,16 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>412</v>
+        <v>466</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10785,10 +10783,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>414</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>414</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10811,16 +10809,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>183</v>
+        <v>468</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>415</v>
+        <v>469</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>416</v>
+        <v>470</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>417</v>
+        <v>471</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10846,13 +10844,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10870,7 +10868,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>414</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10885,27 +10883,27 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>420</v>
+        <v>472</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>421</v>
+        <v>473</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>422</v>
+        <v>474</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10928,16 +10926,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10987,7 +10985,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11002,16 +11000,16 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>431</v>
+        <v>479</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11019,10 +11017,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11033,7 +11031,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11042,20 +11040,18 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>433</v>
+        <v>481</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>434</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11104,13 +11100,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11119,13 +11115,13 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11136,10 +11132,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>439</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>439</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11150,7 +11146,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11159,20 +11155,18 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>440</v>
+        <v>487</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11221,19 +11215,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>439</v>
+        <v>172</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11242,7 +11236,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>438</v>
+        <v>173</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11253,10 +11247,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>489</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>489</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11276,20 +11270,18 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>443</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11326,19 +11318,17 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>179</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11350,16 +11340,16 @@
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11370,12 +11360,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11384,7 +11376,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11393,21 +11385,19 @@
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>150</v>
+        <v>494</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11455,28 +11445,28 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>448</v>
+        <v>179</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11487,12 +11477,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>454</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11513,17 +11505,15 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>183</v>
+        <v>500</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>501</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11548,13 +11538,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11572,19 +11562,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>454</v>
+        <v>179</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11593,7 +11583,7 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11604,14 +11594,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11624,24 +11614,26 @@
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>462</v>
+        <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11689,7 +11681,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>461</v>
+        <v>507</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11701,16 +11693,16 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>466</v>
+        <v>134</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11721,10 +11713,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11735,7 +11727,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11747,16 +11739,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>471</v>
+        <v>511</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11806,13 +11798,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -11821,13 +11813,13 @@
         <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11838,10 +11830,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>513</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>475</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11852,7 +11844,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11864,17 +11856,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>476</v>
+        <v>169</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>477</v>
+        <v>170</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11923,19 +11913,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>475</v>
+        <v>172</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11944,7 +11934,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>479</v>
+        <v>173</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11955,21 +11945,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -11981,15 +11971,17 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>481</v>
+        <v>137</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>482</v>
+        <v>138</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12038,28 +12030,28 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>480</v>
+        <v>179</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>485</v>
+        <v>173</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12070,42 +12062,46 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>486</v>
+        <v>515</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>486</v>
+        <v>515</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12153,19 +12149,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>165</v>
+        <v>507</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12174,7 +12170,7 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12185,10 +12181,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12199,7 +12195,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12211,15 +12207,17 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>137</v>
+        <v>517</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12256,29 +12254,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AC84" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>171</v>
+        <v>516</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>142</v>
+        <v>521</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12287,25 +12287,23 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12314,7 +12312,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12326,15 +12324,17 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12383,19 +12383,19 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>171</v>
+        <v>524</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12404,7 +12404,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12415,14 +12415,12 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>498</v>
+        <v>529</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12443,15 +12441,17 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>501</v>
+        <v>530</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12500,19 +12500,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>171</v>
+        <v>529</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12521,7 +12521,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12532,45 +12532,45 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>503</v>
+        <v>532</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>503</v>
+        <v>532</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>505</v>
+        <v>533</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>140</v>
+        <v>535</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>146</v>
+        <v>536</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12619,28 +12619,28 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>134</v>
+        <v>538</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12651,10 +12651,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12677,17 +12677,15 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>481</v>
+        <v>169</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>509</v>
+        <v>170</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12736,7 +12734,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>508</v>
+        <v>172</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12748,7 +12746,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12757,7 +12755,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>512</v>
+        <v>173</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12768,21 +12766,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12794,15 +12792,17 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12839,31 +12839,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12872,7 +12872,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12883,21 +12883,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -12906,19 +12906,19 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>137</v>
+        <v>380</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>138</v>
+        <v>542</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>168</v>
+        <v>543</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>140</v>
+        <v>544</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12968,19 +12968,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>171</v>
+        <v>545</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -12989,61 +12989,61 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>166</v>
+        <v>547</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>137</v>
+        <v>380</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13087,19 +13087,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>507</v>
+        <v>554</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13108,21 +13108,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>134</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13145,16 +13145,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>520</v>
+        <v>561</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13204,7 +13204,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13213,33 +13213,33 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>521</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>523</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13262,13 +13262,13 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>526</v>
+        <v>566</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>527</v>
+        <v>567</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>520</v>
@@ -13321,7 +13321,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13330,10 +13330,10 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>103</v>
+        <v>521</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13342,21 +13342,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13382,13 +13382,13 @@
         <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>530</v>
+        <v>569</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>531</v>
+        <v>570</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>520</v>
+        <v>571</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13438,7 +13438,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13456,10 +13456,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>528</v>
+        <v>573</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13470,10 +13470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>532</v>
+        <v>574</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>532</v>
+        <v>574</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13496,20 +13496,16 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>533</v>
+        <v>170</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13557,7 +13553,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>532</v>
+        <v>172</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13569,16 +13565,16 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>538</v>
+        <v>173</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13589,21 +13585,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>539</v>
+        <v>575</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>539</v>
+        <v>575</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13615,15 +13611,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13660,31 +13658,31 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13693,7 +13691,7 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13704,21 +13702,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>540</v>
+        <v>576</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>540</v>
+        <v>576</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13727,21 +13725,23 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>137</v>
+        <v>577</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>138</v>
+        <v>578</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>168</v>
+        <v>579</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13777,31 +13777,31 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>171</v>
+        <v>582</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13810,21 +13810,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>166</v>
+        <v>583</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>541</v>
+        <v>585</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>541</v>
+        <v>585</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13841,28 +13841,30 @@
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>380</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13882,13 +13884,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13906,7 +13908,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13915,7 +13917,7 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>103</v>
@@ -13927,21 +13929,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>547</v>
+        <v>593</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>548</v>
+        <v>594</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>549</v>
+        <v>595</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>549</v>
+        <v>595</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13964,26 +13966,24 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>380</v>
+        <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>550</v>
+        <v>596</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q99" t="s" s="2">
-        <v>553</v>
-      </c>
+      <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14025,7 +14025,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>554</v>
+        <v>600</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14034,7 +14034,7 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -14046,21 +14046,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>556</v>
+        <v>602</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>557</v>
+        <v>603</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>557</v>
+        <v>603</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14080,27 +14080,27 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>558</v>
+        <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>559</v>
+        <v>604</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14142,7 +14142,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>557</v>
+        <v>608</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14151,7 +14151,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14160,24 +14160,24 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>563</v>
+        <v>610</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>564</v>
+        <v>602</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14197,27 +14197,29 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>517</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>566</v>
+        <v>612</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>567</v>
+        <v>613</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14259,7 +14261,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>565</v>
+        <v>617</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14268,10 +14270,10 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>521</v>
+        <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14280,21 +14282,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>522</v>
+        <v>618</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>523</v>
+        <v>602</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>568</v>
+        <v>619</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>568</v>
+        <v>619</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14317,16 +14319,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>525</v>
+        <v>620</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>569</v>
+        <v>621</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>570</v>
+        <v>622</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>571</v>
+        <v>376</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14376,7 +14378,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>568</v>
+        <v>619</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14394,13 +14396,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>573</v>
+        <v>623</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14408,10 +14410,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>574</v>
+        <v>624</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>574</v>
+        <v>624</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14434,13 +14436,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>162</v>
+        <v>481</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>163</v>
+        <v>625</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>164</v>
+        <v>626</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14491,7 +14493,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>165</v>
+        <v>624</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14503,16 +14505,16 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>166</v>
+        <v>628</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14523,21 +14525,21 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>575</v>
+        <v>629</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>575</v>
+        <v>629</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14549,17 +14551,15 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14596,31 +14596,31 @@
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -14629,7 +14629,7 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -14640,21 +14640,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>576</v>
+        <v>630</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>576</v>
+        <v>630</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -14663,23 +14663,21 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>577</v>
+        <v>137</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>578</v>
+        <v>138</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>579</v>
+        <v>176</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14727,19 +14725,19 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>582</v>
+        <v>179</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
@@ -14748,32 +14746,32 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>583</v>
+        <v>173</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>584</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>585</v>
+        <v>631</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>585</v>
+        <v>631</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -14785,24 +14783,24 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>586</v>
+        <v>505</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O106" t="s" s="2">
-        <v>588</v>
+        <v>146</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q106" t="s" s="2">
-        <v>589</v>
-      </c>
+      <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
         <v>82</v>
       </c>
@@ -14822,13 +14820,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -14846,19 +14844,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>592</v>
+        <v>507</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -14867,21 +14865,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>593</v>
+        <v>134</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>595</v>
+        <v>632</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>595</v>
+        <v>632</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14889,7 +14887,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>91</v>
@@ -14901,27 +14899,27 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>82</v>
@@ -14939,13 +14937,11 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14963,10 +14959,10 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>91</v>
@@ -14981,24 +14977,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>601</v>
+        <v>636</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>602</v>
+        <v>637</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>603</v>
+        <v>638</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>603</v>
+        <v>638</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15018,27 +15014,27 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>604</v>
+        <v>639</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>82</v>
@@ -15056,13 +15052,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>82</v>
+        <v>642</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15080,7 +15076,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>608</v>
+        <v>638</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15089,7 +15085,7 @@
         <v>91</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>103</v>
@@ -15098,24 +15094,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>602</v>
+        <v>646</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>611</v>
+        <v>647</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>611</v>
+        <v>647</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15135,29 +15131,27 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>111</v>
+        <v>648</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>615</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>82</v>
@@ -15199,7 +15193,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>617</v>
+        <v>647</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15214,38 +15208,38 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>618</v>
+        <v>652</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>619</v>
+        <v>653</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>619</v>
+        <v>653</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15257,16 +15251,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>620</v>
+        <v>655</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>621</v>
+        <v>656</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>622</v>
+        <v>657</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>376</v>
+        <v>658</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15316,13 +15310,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>619</v>
+        <v>653</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15337,10 +15331,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>623</v>
+        <v>659</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15348,10 +15342,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15362,7 +15356,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15374,15 +15368,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>481</v>
+        <v>661</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>625</v>
+        <v>662</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15431,13 +15427,13 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
@@ -15446,952 +15442,18 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>628</v>
+        <v>666</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y115" s="2"/>
-      <c r="Z115" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO119" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/feature/add-prescritionid-invariant/StructureDefinition-jp-medicationrequest.xlsx
@@ -502,7 +502,7 @@
 　- requestIdentifier : 処方オーダに対するID  
 　- prescriptionIdentifierCommon : 全国で⼀意になる発番ルールにもとづき発行される処方箋ID  
 [invariantで定義される識別子]  
-　- valid-system-local-prescriptionID : 医療機関毎に管理される処方箋に対するID  </t>
+　- jp-inv-local-prescriptionid : 医療機関毎に管理される処方箋に対するID  </t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
